--- a/results/tables/final_results.xlsx
+++ b/results/tables/final_results.xlsx
@@ -499,43 +499,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00443073471676949</v>
+        <v>0.003679741205014153</v>
       </c>
       <c r="C2" t="n">
-        <v>0.008593834651302317</v>
+        <v>0.008249234754499535</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007575185398160834</v>
+        <v>0.006894104651002251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004915404748551132</v>
+        <v>0.004756649593386351</v>
       </c>
       <c r="F2" t="n">
-        <v>0.003897924845765564</v>
+        <v>0.00276991508289527</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01457146892240624</v>
+        <v>0.01200825210392487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009643865596341247</v>
+        <v>0.008047674077217867</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005393921445782775</v>
+        <v>0.004968780777725716</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003049635445877734</v>
+        <v>0.002254346947027902</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02238998106217765</v>
+        <v>0.01873744678813018</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01204303300964376</v>
+        <v>0.01006591760001697</v>
       </c>
       <c r="M2" t="n">
-        <v>0.005895382132833762</v>
+        <v>0.005392887334520511</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7601473296500921</v>
+        <v>0.6793332757578374</v>
       </c>
     </row>
     <row r="3">
@@ -545,43 +545,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.004627033090297251</v>
+        <v>0.003639304488475536</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00894967253343016</v>
+        <v>0.008025407160069432</v>
       </c>
       <c r="D3" t="n">
-        <v>0.007501185825347018</v>
+        <v>0.006617273545374502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.004662203215554309</v>
+        <v>0.004469268095430651</v>
       </c>
       <c r="F3" t="n">
-        <v>0.003883903533370724</v>
+        <v>0.002921552769915083</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01495197082308645</v>
+        <v>0.01272425209964585</v>
       </c>
       <c r="H3" t="n">
-        <v>0.009509686991055194</v>
+        <v>0.00810188567782978</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00509300483737044</v>
+        <v>0.004806743294957678</v>
       </c>
       <c r="J3" t="n">
-        <v>0.003042624789680314</v>
+        <v>0.002350384148807117</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02321948432269404</v>
+        <v>0.01955748939369906</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01200924042201652</v>
+        <v>0.01016547589994456</v>
       </c>
       <c r="M3" t="n">
-        <v>0.005632157995465338</v>
+        <v>0.005229753289808261</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7552117863720074</v>
+        <v>0.6726401243630711</v>
       </c>
     </row>
     <row r="4">
@@ -591,43 +591,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001177790241166573</v>
+        <v>0.0006672058228871815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00243829394031179</v>
+        <v>0.001051516624707082</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002087802094359073</v>
+        <v>0.0009179153870411152</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001408986103321493</v>
+        <v>0.0005221952644111965</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001009534492428491</v>
+        <v>0.0005560048524059847</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003933593417944414</v>
+        <v>0.001796186599563066</v>
       </c>
       <c r="H4" t="n">
-        <v>0.002618454254062018</v>
+        <v>0.001157146090903879</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001550091323997662</v>
+        <v>0.0005638887513490367</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009885025238362312</v>
+        <v>0.0006217145167812374</v>
       </c>
       <c r="K4" t="n">
-        <v>0.007105395396242068</v>
+        <v>0.004512695591273768</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003653153618783814</v>
+        <v>0.001989249846331516</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001767066079383618</v>
+        <v>0.0007366546577039288</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9237569060773481</v>
+        <v>0.9378616460834269</v>
       </c>
     </row>
     <row r="5">
@@ -637,43 +637,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009534492428491308</v>
+        <v>0.0006672058228871816</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001840685759993107</v>
+        <v>0.001432335411813778</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001745984882192012</v>
+        <v>0.001057734873715959</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001214011964853244</v>
+        <v>0.0006789156220514894</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0008412787436904094</v>
+        <v>0.0006368782854832188</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00287746478224483</v>
+        <v>0.002576849237523651</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002132039697349281</v>
+        <v>0.001483660661685625</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001294360373093381</v>
+        <v>0.0008058259359816172</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0009955131800336511</v>
+        <v>0.0006217145167812374</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006934570506385794</v>
+        <v>0.004909352640024599</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003430053846157275</v>
+        <v>0.002222820569704729</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001558681492142091</v>
+        <v>0.0009704487517841294</v>
       </c>
       <c r="N5" t="n">
-        <v>0.930828729281768</v>
+        <v>0.9499956818378098</v>
       </c>
     </row>
     <row r="6">
@@ -683,43 +683,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003505328098710039</v>
+        <v>0.003315810756166599</v>
       </c>
       <c r="C6" t="n">
-        <v>0.007270951655904015</v>
+        <v>0.006950044545588807</v>
       </c>
       <c r="D6" t="n">
-        <v>0.006178533979956621</v>
+        <v>0.00591330493873267</v>
       </c>
       <c r="E6" t="n">
-        <v>0.004180415342431606</v>
+        <v>0.004014663925955879</v>
       </c>
       <c r="F6" t="n">
-        <v>0.003140773976444195</v>
+        <v>0.002769915082895269</v>
       </c>
       <c r="G6" t="n">
-        <v>0.01230471953946972</v>
+        <v>0.01182591222510352</v>
       </c>
       <c r="H6" t="n">
-        <v>0.008024512593648839</v>
+        <v>0.00760346359864959</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00470452866134302</v>
+        <v>0.004510148760047667</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00269910263600673</v>
+        <v>0.002259401536595229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0212424239797573</v>
+        <v>0.01933611385650451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01068693431640566</v>
+        <v>0.009832591747252902</v>
       </c>
       <c r="M6" t="n">
-        <v>0.005252376356940867</v>
+        <v>0.004981981832440753</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04677716390423572</v>
+        <v>0.02141808446325244</v>
       </c>
     </row>
     <row r="7">
@@ -729,43 +729,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003729669097027482</v>
+        <v>0.003356247472705217</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007825041736073738</v>
+        <v>0.006863971670452875</v>
       </c>
       <c r="D7" t="n">
-        <v>0.006558424055099332</v>
+        <v>0.006048669943677737</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004383685424066803</v>
+        <v>0.004166807071932425</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003224901850813236</v>
+        <v>0.00267893247068338</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01281886973463506</v>
+        <v>0.01117417449429339</v>
       </c>
       <c r="H7" t="n">
-        <v>0.008299552051325631</v>
+        <v>0.007490557426595526</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004835851883752192</v>
+        <v>0.004546484974229617</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00267807066741447</v>
+        <v>0.002213910230489284</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02178592450627519</v>
+        <v>0.0193941190504187</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0109262911244198</v>
+        <v>0.009876798420012382</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005378495424331916</v>
+        <v>0.005075473106788156</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04640883977900553</v>
+        <v>0.02176353743846619</v>
       </c>
     </row>
     <row r="8">
@@ -775,43 +775,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.005047672462142457</v>
+        <v>0.004569348968863729</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01008459596718037</v>
+        <v>0.01012464415941003</v>
       </c>
       <c r="D8" t="n">
-        <v>0.008709706426150874</v>
+        <v>0.008375079827942923</v>
       </c>
       <c r="E8" t="n">
-        <v>0.005880071041316134</v>
+        <v>0.005777704767039583</v>
       </c>
       <c r="F8" t="n">
-        <v>0.004304542905215929</v>
+        <v>0.003801051354630004</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01757728885919432</v>
+        <v>0.01670493221159688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01128426437670183</v>
+        <v>0.01068617466103278</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006614066542520292</v>
+        <v>0.006493105365995075</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00353337072349972</v>
+        <v>0.00306813586736757</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02776331168200633</v>
+        <v>0.02623544302987464</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01442266496229813</v>
+        <v>0.01354787413885656</v>
       </c>
       <c r="M8" t="n">
-        <v>0.007282855188178318</v>
+        <v>0.007125442604425262</v>
       </c>
       <c r="N8" t="n">
-        <v>0.340036832412523</v>
+        <v>0.1908195871836946</v>
       </c>
     </row>
     <row r="9">
@@ -821,43 +821,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004907459338194055</v>
+        <v>0.004528912252325112</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00966443420278946</v>
+        <v>0.01019633724818763</v>
       </c>
       <c r="D9" t="n">
-        <v>0.008566215222980119</v>
+        <v>0.008354614983718148</v>
       </c>
       <c r="E9" t="n">
-        <v>0.005878045740636879</v>
+        <v>0.00577225704272813</v>
       </c>
       <c r="F9" t="n">
-        <v>0.004178351093662367</v>
+        <v>0.003801051354630004</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01673717855820347</v>
+        <v>0.01633414504845226</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01102069964663584</v>
+        <v>0.01057754469425044</v>
       </c>
       <c r="I9" t="n">
-        <v>0.006578360682311186</v>
+        <v>0.00644876132373244</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00353337072349972</v>
+        <v>0.00306813586736757</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02798317068700647</v>
+        <v>0.02662530753676182</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01445461853985258</v>
+        <v>0.01361029033727857</v>
       </c>
       <c r="M9" t="n">
-        <v>0.007328451796098642</v>
+        <v>0.007143650846104349</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3351749539594843</v>
+        <v>0.188919595820019</v>
       </c>
     </row>
   </sheetData>
@@ -953,43 +953,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004150308468872686</v>
+        <v>0.003012535382126972</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00824994440016366</v>
+        <v>0.006363474783876498</v>
       </c>
       <c r="D2" t="n">
-        <v>0.007327140451084468</v>
+        <v>0.00542372413538514</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004924635445877734</v>
+        <v>0.003688109358853394</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00353337072349972</v>
+        <v>0.002375657096643753</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01356845459942231</v>
+        <v>0.009970917257873536</v>
       </c>
       <c r="H2" t="n">
-        <v>0.009246221066990325</v>
+        <v>0.006668124796271293</v>
       </c>
       <c r="I2" t="n">
-        <v>0.005486354735388266</v>
+        <v>0.004036010827366396</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002776219854178351</v>
+        <v>0.001976344520824909</v>
       </c>
       <c r="K2" t="n">
-        <v>0.02181576142852116</v>
+        <v>0.01674075179785747</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01164631678610497</v>
+        <v>0.008655728529030245</v>
       </c>
       <c r="M2" t="n">
-        <v>0.005992293347188655</v>
+        <v>0.004472656849111382</v>
       </c>
       <c r="N2" t="n">
-        <v>0.870791896869245</v>
+        <v>0.8163917436738924</v>
       </c>
     </row>
     <row r="3">
@@ -999,89 +999,89 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005047672462142457</v>
+        <v>0.004569348968863729</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01008459596718037</v>
+        <v>0.01012464415941003</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008709706426150874</v>
+        <v>0.008375079827942923</v>
       </c>
       <c r="E3" t="n">
-        <v>0.005880071041316134</v>
+        <v>0.005777704767039583</v>
       </c>
       <c r="F3" t="n">
-        <v>0.004304542905215929</v>
+        <v>0.003801051354630004</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01757728885919432</v>
+        <v>0.01670493221159688</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01128426437670183</v>
+        <v>0.01068617466103278</v>
       </c>
       <c r="I3" t="n">
-        <v>0.006614066542520292</v>
+        <v>0.006493105365995075</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00353337072349972</v>
+        <v>0.00306813586736757</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02776331168200633</v>
+        <v>0.02623544302987464</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01442266496229813</v>
+        <v>0.01354787413885656</v>
       </c>
       <c r="M3" t="n">
-        <v>0.007282855188178318</v>
+        <v>0.007125442604425262</v>
       </c>
       <c r="N3" t="n">
-        <v>0.340036832412523</v>
+        <v>0.1908195871836946</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>alpha_a0.65</t>
+          <t>alpha_a0.75</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006421761076836793</v>
+        <v>0.005438738374443995</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01354634949321069</v>
+        <v>0.01175462227239153</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01128994473362362</v>
+        <v>0.01005427365508404</v>
       </c>
       <c r="E4" t="n">
-        <v>0.007445511622110052</v>
+        <v>0.006989683021072021</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005412226584408302</v>
+        <v>0.004720986655883543</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02180830767432416</v>
+        <v>0.0209335574489769</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01421608897165758</v>
+        <v>0.0132360494670443</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008317737449459335</v>
+        <v>0.00799994671285866</v>
       </c>
       <c r="J4" t="n">
-        <v>0.004199383062254628</v>
+        <v>0.003634249898908209</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03428352071230741</v>
+        <v>0.03093045429245458</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01791625731402405</v>
+        <v>0.01628693840127944</v>
       </c>
       <c r="M4" t="n">
-        <v>0.009158689256841591</v>
+        <v>0.008688213521018385</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6584162062615101</v>
+        <v>0.3428188962777442</v>
       </c>
     </row>
     <row r="5">
@@ -1091,43 +1091,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006505888951205833</v>
+        <v>0.005438738374443995</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01309568344421884</v>
+        <v>0.01175462227239153</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01117605024907388</v>
+        <v>0.01005427365508404</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007336807502960055</v>
+        <v>0.006989683021072021</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005272013460459899</v>
+        <v>0.004720986655883543</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02152122636373904</v>
+        <v>0.0209335574489769</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0139751270974001</v>
+        <v>0.0132360494670443</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0081135581595489</v>
+        <v>0.00799994671285866</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004213404374649466</v>
+        <v>0.003634249898908209</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0344561936134073</v>
+        <v>0.03093045429245458</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01780042450229971</v>
+        <v>0.01628693840127944</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008982357731756143</v>
+        <v>0.008688213521018385</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7372375690607735</v>
+        <v>0.3428188962777442</v>
       </c>
     </row>
     <row r="6">
@@ -1137,43 +1137,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.006590016825574875</v>
+        <v>0.005438738374443995</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01368157387380211</v>
+        <v>0.01175462227239153</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01162333086750194</v>
+        <v>0.01005427365508404</v>
       </c>
       <c r="E6" t="n">
-        <v>0.007705178538044494</v>
+        <v>0.006989683021072021</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00537016264722378</v>
+        <v>0.004720986655883543</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02180697855248186</v>
+        <v>0.0209335574489769</v>
       </c>
       <c r="H6" t="n">
-        <v>0.01435778517140306</v>
+        <v>0.0132360494670443</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008443147605524417</v>
+        <v>0.00799994671285866</v>
       </c>
       <c r="J6" t="n">
-        <v>0.004395681435782389</v>
+        <v>0.003634249898908209</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03618053459552267</v>
+        <v>0.03093045429245458</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01860151395829026</v>
+        <v>0.01628693840127944</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00939725562628985</v>
+        <v>0.008688213521018385</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6561325966850828</v>
+        <v>0.3428188962777442</v>
       </c>
     </row>
   </sheetData>
@@ -1269,43 +1269,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00263600673022995</v>
+        <v>0.001496158511928831</v>
       </c>
       <c r="C2" t="n">
-        <v>0.004518599634089885</v>
+        <v>0.003000012448051267</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003794319332714121</v>
+        <v>0.002458753996436174</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00218385835358634</v>
+        <v>0.00155855461203217</v>
       </c>
       <c r="F2" t="n">
-        <v>0.002131239484015704</v>
+        <v>0.001344520824909017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.007139978279885427</v>
+        <v>0.005707840429338238</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004726920956454316</v>
+        <v>0.003400300959517137</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00238148347922705</v>
+        <v>0.001844273087617878</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00173163208076276</v>
+        <v>0.001197937727456531</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01262776498389959</v>
+        <v>0.009968675677217572</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006337260983769844</v>
+        <v>0.004699640737174539</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002737758275508938</v>
+        <v>0.002134050779787677</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8575322283609577</v>
+        <v>0.8308575870109681</v>
       </c>
     </row>
     <row r="3">
@@ -1315,43 +1315,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003000560852495793</v>
+        <v>0.002102709260008087</v>
       </c>
       <c r="C3" t="n">
-        <v>0.006163011429581321</v>
+        <v>0.004497565201788459</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0048330301978177</v>
+        <v>0.003761592244282096</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002929636380631894</v>
+        <v>0.002538105989127016</v>
       </c>
       <c r="F3" t="n">
-        <v>0.002523836231071228</v>
+        <v>0.001718560452891225</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01005630212057953</v>
+        <v>0.00759557517656754</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006198959346570778</v>
+        <v>0.004800676903066115</v>
       </c>
       <c r="I3" t="n">
-        <v>0.003275885562986957</v>
+        <v>0.002822315665269567</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002040100953449243</v>
+        <v>0.001465830974524869</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01586579333330153</v>
+        <v>0.0128390762237946</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00796268860958994</v>
+        <v>0.006351700957954717</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003655483639567426</v>
+        <v>0.003171575265601611</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8570902394106814</v>
+        <v>0.8219189912773124</v>
       </c>
     </row>
     <row r="4">
@@ -1361,43 +1361,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003813796971396523</v>
+        <v>0.002446421350586333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.007820204630428229</v>
+        <v>0.0053114208842601</v>
       </c>
       <c r="D4" t="n">
-        <v>0.006496087740776553</v>
+        <v>0.004508204507064237</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004212781205209696</v>
+        <v>0.003050135912297254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003182837913628716</v>
+        <v>0.002163364334816013</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01335575946083941</v>
+        <v>0.009389888093586362</v>
       </c>
       <c r="H4" t="n">
-        <v>0.008380531696306716</v>
+        <v>0.0059325344349327</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004763768441258226</v>
+        <v>0.00347361468587375</v>
       </c>
       <c r="J4" t="n">
-        <v>0.002495793606281548</v>
+        <v>0.001824706833805095</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01971784614812732</v>
+        <v>0.01552943859385021</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01032669565024159</v>
+        <v>0.007778873984779219</v>
       </c>
       <c r="M4" t="n">
-        <v>0.005188780418323848</v>
+        <v>0.003887789830443772</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8631307550644567</v>
+        <v>0.8106485879609638</v>
       </c>
     </row>
     <row r="5">
@@ -1407,43 +1407,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002383623107122827</v>
+        <v>0.00137484836231298</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003794428987722282</v>
+        <v>0.003046146861709537</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00337891658342295</v>
+        <v>0.002610325928480082</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001949936125132424</v>
+        <v>0.001771465157029249</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002005047672462143</v>
+        <v>0.001415285078851597</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007157061286984697</v>
+        <v>0.006232287492491423</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004507951494411832</v>
+        <v>0.003738102450340879</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002247466810928272</v>
+        <v>0.002084104893698505</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001689568143578239</v>
+        <v>0.001142337242215932</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01253832374153764</v>
+        <v>0.009024558842231639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006104786689002171</v>
+        <v>0.004628532285964567</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002603395288586377</v>
+        <v>0.002265082091058871</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8422099447513812</v>
+        <v>0.8148803869073322</v>
       </c>
     </row>
     <row r="6">
@@ -1453,43 +1453,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003056646102075154</v>
+        <v>0.002082490901738779</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00576502119290036</v>
+        <v>0.00438902018265021</v>
       </c>
       <c r="D6" t="n">
-        <v>0.005034857720547281</v>
+        <v>0.003722308129120149</v>
       </c>
       <c r="E6" t="n">
-        <v>0.003227978749922104</v>
+        <v>0.002487475850294289</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002481772293886708</v>
+        <v>0.001809543065103114</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00954330551221683</v>
+        <v>0.007731607508658859</v>
       </c>
       <c r="H6" t="n">
-        <v>0.006300592939341147</v>
+        <v>0.004894719988802928</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003542651894371509</v>
+        <v>0.002823336834996088</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001948962422882782</v>
+        <v>0.001496158511928831</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01447892936981566</v>
+        <v>0.01249081705857337</v>
       </c>
       <c r="L6" t="n">
-        <v>0.007835987187033816</v>
+        <v>0.00631172704427603</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003872146761894011</v>
+        <v>0.003132971335018225</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8467034990791897</v>
+        <v>0.7945850246135245</v>
       </c>
     </row>
     <row r="7">
@@ -1499,43 +1499,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.003757711721817163</v>
+        <v>0.002567731500202184</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00743937661848265</v>
+        <v>0.005598977554499746</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00639162579767129</v>
+        <v>0.004629119585232916</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004212975945659624</v>
+        <v>0.003079115559149931</v>
       </c>
       <c r="F7" t="n">
-        <v>0.003112731351654515</v>
+        <v>0.002153255155681359</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01279175908262142</v>
+        <v>0.009231189180397784</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00824981552791478</v>
+        <v>0.00592023168895525</v>
       </c>
       <c r="I7" t="n">
-        <v>0.004763616976463837</v>
+        <v>0.003463295121705959</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002467750981491868</v>
+        <v>0.001683178325919935</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0200091049821082</v>
+        <v>0.0144426280058079</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01038333818174011</v>
+        <v>0.007443007940635791</v>
       </c>
       <c r="M7" t="n">
-        <v>0.005238205473478595</v>
+        <v>0.003806086133282894</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8597421731123388</v>
+        <v>0.802789532774851</v>
       </c>
     </row>
     <row r="8">
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.003084688726864835</v>
+        <v>0.002325111200970481</v>
       </c>
       <c r="C8" t="n">
-        <v>0.006018355343643866</v>
+        <v>0.004839709879195144</v>
       </c>
       <c r="D8" t="n">
-        <v>0.005376151935940765</v>
+        <v>0.00415993096832604</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003587975945659625</v>
+        <v>0.002834529586197601</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002537857543466069</v>
+        <v>0.001799433885968459</v>
       </c>
       <c r="G8" t="n">
-        <v>0.009838314189984919</v>
+        <v>0.007247624064371426</v>
       </c>
       <c r="H8" t="n">
-        <v>0.006729212665966689</v>
+        <v>0.005021529964821376</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003979067627237846</v>
+        <v>0.003085293199815757</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002110207515423444</v>
+        <v>0.001496158511928831</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01665686825757013</v>
+        <v>0.0126520975465845</v>
       </c>
       <c r="L8" t="n">
-        <v>0.008749792513510607</v>
+        <v>0.006571081748048878</v>
       </c>
       <c r="M8" t="n">
-        <v>0.004425332350553242</v>
+        <v>0.003433667816758336</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8623941068139963</v>
+        <v>0.8022713533120304</v>
       </c>
     </row>
     <row r="9">
@@ -1591,43 +1591,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003533370723499719</v>
+        <v>0.002689041649818035</v>
       </c>
       <c r="C9" t="n">
-        <v>0.006669430167002154</v>
+        <v>0.005730722901823339</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006157400789362485</v>
+        <v>0.004683065840744698</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004147971583473547</v>
+        <v>0.00310691580177023</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002916432978126753</v>
+        <v>0.002153255155681359</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01126774200985806</v>
+        <v>0.008948780482469117</v>
       </c>
       <c r="H9" t="n">
-        <v>0.007715807142280552</v>
+        <v>0.005795402905564295</v>
       </c>
       <c r="I9" t="n">
-        <v>0.004577330823274658</v>
+        <v>0.003412991846968677</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002404655075715087</v>
+        <v>0.001733724221593207</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01855929010090994</v>
+        <v>0.0138707927706198</v>
       </c>
       <c r="L9" t="n">
-        <v>0.009901487818586314</v>
+        <v>0.007279241180607601</v>
       </c>
       <c r="M9" t="n">
-        <v>0.00504619215806584</v>
+        <v>0.003732327569352736</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8609944751381216</v>
+        <v>0.7910441316175836</v>
       </c>
     </row>
     <row r="10">
@@ -1637,43 +1637,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.003505328098710039</v>
+        <v>0.002689041649818035</v>
       </c>
       <c r="C10" t="n">
-        <v>0.006842096004360677</v>
+        <v>0.005384779803269693</v>
       </c>
       <c r="D10" t="n">
-        <v>0.006171327398075238</v>
+        <v>0.004716785118996147</v>
       </c>
       <c r="E10" t="n">
-        <v>0.004131886022309466</v>
+        <v>0.003206098081502449</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002972518227706114</v>
+        <v>0.002153255155681359</v>
       </c>
       <c r="G10" t="n">
-        <v>0.01126672371024752</v>
+        <v>0.008858186970869918</v>
       </c>
       <c r="H10" t="n">
-        <v>0.007787995453645092</v>
+        <v>0.00588313325111972</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004615248555228992</v>
+        <v>0.003512671928635767</v>
       </c>
       <c r="J10" t="n">
-        <v>0.002614974761637689</v>
+        <v>0.00176405175899717</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01888680792553562</v>
+        <v>0.01452925994101071</v>
       </c>
       <c r="L10" t="n">
-        <v>0.01019058122427779</v>
+        <v>0.007522779196072229</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005105653329049002</v>
+        <v>0.00385416290665545</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8575322283609577</v>
+        <v>0.7972622851714311</v>
       </c>
     </row>
     <row r="11">
@@ -1683,43 +1683,43 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.004150308468872686</v>
+        <v>0.003012535382126972</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00824994440016366</v>
+        <v>0.006363474783876498</v>
       </c>
       <c r="D11" t="n">
-        <v>0.007327140451084468</v>
+        <v>0.00542372413538514</v>
       </c>
       <c r="E11" t="n">
-        <v>0.004924635445877734</v>
+        <v>0.003688109358853394</v>
       </c>
       <c r="F11" t="n">
-        <v>0.00353337072349972</v>
+        <v>0.002375657096643753</v>
       </c>
       <c r="G11" t="n">
-        <v>0.01356845459942231</v>
+        <v>0.009970917257873536</v>
       </c>
       <c r="H11" t="n">
-        <v>0.009246221066990325</v>
+        <v>0.006668124796271293</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005486354735388266</v>
+        <v>0.004036010827366396</v>
       </c>
       <c r="J11" t="n">
-        <v>0.002776219854178351</v>
+        <v>0.001976344520824909</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02181576142852116</v>
+        <v>0.01674075179785747</v>
       </c>
       <c r="L11" t="n">
-        <v>0.01164631678610497</v>
+        <v>0.008655728529030245</v>
       </c>
       <c r="M11" t="n">
-        <v>0.005992293347188655</v>
+        <v>0.004472656849111382</v>
       </c>
       <c r="N11" t="n">
-        <v>0.870791896869245</v>
+        <v>0.8163917436738924</v>
       </c>
     </row>
   </sheetData>
@@ -1744,132 +1744,132 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>MAP@20_mean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>MAP@20_std</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>R@20_mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>R@20_std</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>R@10_mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>R@10_std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>P@5_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>P@5_std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NDCG@10_mean</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>NDCG@10_std</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>R@5_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>R@5_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>NDCG@20_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>NDCG@20_std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>NDCG@5_mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>NDCG@5_std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>P@10_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>P@10_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>MAP@5_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>MAP@5_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Coverage_mean</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Coverage_std</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>MAP@10_mean</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>MAP@10_std</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>P@20_mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>P@20_std</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>R@5_mean</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>R@5_std</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>MAP@20_mean</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>MAP@20_std</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Coverage_mean</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Coverage_std</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>NDCG@20_mean</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>NDCG@20_std</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>P@5_mean</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>P@5_std</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>MAP@5_mean</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>MAP@5_std</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>MAP@10_mean</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>MAP@10_std</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>R@10_mean</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>R@10_std</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>R@20_mean</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>R@20_std</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>P@10_mean</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>P@10_std</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>NDCG@10_mean</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>NDCG@10_std</t>
         </is>
       </c>
     </row>
@@ -1880,82 +1880,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0100598858887486</v>
+        <v>0.007972256122618758</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002701367306688581</v>
+        <v>0.0002576845951726161</v>
       </c>
       <c r="D2" t="n">
-        <v>0.003327597561657695</v>
+        <v>0.02981475611769078</v>
       </c>
       <c r="E2" t="n">
-        <v>4.983130121397895e-05</v>
+        <v>0.001153452181141216</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0131634693029357</v>
+        <v>0.01884546119394819</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0005374022605894914</v>
+        <v>0.0006345557479963481</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008825458803863838</v>
+        <v>0.004448000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002457122091189105</v>
+        <v>0.0002467711490429949</v>
       </c>
       <c r="J2" t="n">
-        <v>0.9321841620626152</v>
+        <v>0.01163101088023312</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009911683648798077</v>
+        <v>0.0002774294891482909</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01668941329173721</v>
+        <v>0.01168364807414807</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0003143617089009231</v>
+        <v>0.0004914041307369717</v>
       </c>
       <c r="N2" t="n">
-        <v>0.005205970377239141</v>
+        <v>0.01491875828277999</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000170142929325716</v>
+        <v>0.0004435006535253096</v>
       </c>
       <c r="P2" t="n">
-        <v>0.006932068797261974</v>
+        <v>0.008976710281052586</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0002224155626415628</v>
+        <v>0.0003313545578495771</v>
       </c>
       <c r="R2" t="n">
-        <v>0.007936826124478819</v>
+        <v>0.003646000000000001</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0002272890811228929</v>
+        <v>0.0001139473562659527</v>
       </c>
       <c r="T2" t="n">
-        <v>0.02107601305891391</v>
+        <v>0.006278111111111111</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0004434430115275915</v>
+        <v>0.0002611879798200316</v>
       </c>
       <c r="V2" t="n">
-        <v>0.03343978829738098</v>
+        <v>0.8102599533638483</v>
       </c>
       <c r="W2" t="n">
-        <v>0.0007316997117570433</v>
+        <v>0.001457467699091738</v>
       </c>
       <c r="X2" t="n">
-        <v>0.004202757065782192</v>
+        <v>0.007184216921768708</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.895576876656785e-05</v>
+        <v>0.0002230996502546447</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.01299658466610852</v>
+        <v>0.002922</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0002475875483462266</v>
+        <v>0.0001117407714310225</v>
       </c>
     </row>
     <row r="3">
@@ -1965,82 +1965,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.007143213231661678</v>
+        <v>0.005235541418334037</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002800930538733769</v>
+        <v>0.0002453311084404361</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002410518320318324</v>
+        <v>0.02056801382780197</v>
       </c>
       <c r="E3" t="n">
-        <v>3.124241667506349e-05</v>
+        <v>0.001210380377531435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.009215474654589408</v>
+        <v>0.01260000334957602</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0003763773611412234</v>
+        <v>0.000357120447464929</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006438093123501706</v>
+        <v>0.00292</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0002290951181806744</v>
+        <v>0.0001697056274847714</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8357274401473298</v>
+        <v>0.007640286298542122</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001078630141744268</v>
+        <v>0.0003663379457127028</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0121987866233729</v>
+        <v>0.007429863681324358</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0001897035293410428</v>
+        <v>0.0002366149521474834</v>
       </c>
       <c r="N3" t="n">
-        <v>0.003579531872786525</v>
+        <v>0.01000311389946677</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0001009898033392601</v>
+        <v>0.0004479937536443689</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00500003308738183</v>
+        <v>0.0057361389479189</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0002657811350475688</v>
+        <v>0.0003412689261348746</v>
       </c>
       <c r="R3" t="n">
-        <v>0.005740385086862274</v>
+        <v>0.002444</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0002339930853847413</v>
+        <v>0.0001028785691968935</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0150723639678908</v>
+        <v>0.004009233333333333</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002419636310772433</v>
+        <v>0.0002434831341282971</v>
       </c>
       <c r="V3" t="n">
-        <v>0.02484315169175494</v>
+        <v>0.6629242594351844</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003440993284601702</v>
+        <v>0.004588888021614309</v>
       </c>
       <c r="X3" t="n">
-        <v>0.002935708013942651</v>
+        <v>0.004670133582136558</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.264191480183957e-05</v>
+        <v>0.0002553058104215972</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0093082242585133</v>
+        <v>0.001994</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0002057914197232308</v>
+        <v>9.712878049270461e-05</v>
       </c>
     </row>
     <row r="4">
@@ -2050,82 +2050,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0119916324699047</v>
+        <v>0.0121534069248422</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006346668555434902</v>
+        <v>0.0003938402808301826</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004176686649524933</v>
+        <v>0.04239207772595709</v>
       </c>
       <c r="E4" t="n">
-        <v>3.799276675735987e-05</v>
+        <v>0.0008418803773485236</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01467423427768743</v>
+        <v>0.02658127498137314</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007160913836699497</v>
+        <v>0.001385726006929579</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01040191552558643</v>
+        <v>0.007000000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0005511467964351665</v>
+        <v>0.000317742033731768</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05190423572744015</v>
+        <v>0.01747388410177285</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001252388687284178</v>
+        <v>0.0006749975763581045</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01984204629655657</v>
+        <v>0.01710675668524391</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0005884412643136154</v>
+        <v>0.0008993656963879808</v>
       </c>
       <c r="N4" t="n">
-        <v>0.006322468669590948</v>
+        <v>0.02225875645434506</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0002531584672029725</v>
+        <v>0.0004724645020128851</v>
       </c>
       <c r="P4" t="n">
-        <v>0.008287121079865402</v>
+        <v>0.01396089526908307</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0005526259112818452</v>
+        <v>0.000553028482337056</v>
       </c>
       <c r="R4" t="n">
-        <v>0.009396999097391515</v>
+        <v>0.005528</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0005652117309690328</v>
+        <v>0.0002531718783751464</v>
       </c>
       <c r="T4" t="n">
-        <v>0.02408493239111678</v>
+        <v>0.009894066666666666</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0008899531689602172</v>
+        <v>0.000430870670564946</v>
       </c>
       <c r="V4" t="n">
-        <v>0.03854714658983302</v>
+        <v>0.02237671646947059</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0006001301624901435</v>
+        <v>0.0005023936288884703</v>
       </c>
       <c r="X4" t="n">
-        <v>0.005194133004728822</v>
+        <v>0.01104135255731922</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.193868056751573e-05</v>
+        <v>0.0004403364439361508</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01545954755472754</v>
+        <v>0.004469000000000001</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0006497201547432348</v>
+        <v>0.0001032666451474046</v>
       </c>
     </row>
     <row r="5">
@@ -2135,82 +2135,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02042063900153978</v>
+        <v>0.02122183368171335</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008662840311143122</v>
+        <v>0.0001410321589915643</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00665657126043015</v>
+        <v>0.07400286297899913</v>
       </c>
       <c r="E5" t="n">
-        <v>4.706515503278844e-05</v>
+        <v>0.000443498391289155</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02615539182606634</v>
+        <v>0.04873855989098663</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001139963908538411</v>
+        <v>0.001606236475605708</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0179039195363804</v>
+        <v>0.01234</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0007473748772035784</v>
+        <v>0.0002802855686616774</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4234843462246777</v>
+        <v>0.03096586053764811</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004075309629678028</v>
+        <v>0.0004928012188564268</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03319342891769571</v>
+        <v>0.03096974816264175</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0008027547575962912</v>
+        <v>0.001089694056792311</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01042779517774696</v>
+        <v>0.038576399235454</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002611289736609273</v>
+        <v>0.0002160572437444974</v>
       </c>
       <c r="P5" t="n">
-        <v>0.01422911466734615</v>
+        <v>0.0243707630028453</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0007702919685273037</v>
+        <v>0.000355125683047624</v>
       </c>
       <c r="R5" t="n">
-        <v>0.01626215767731718</v>
+        <v>0.009836000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0007713586817065417</v>
+        <v>0.000271558465159899</v>
       </c>
       <c r="T5" t="n">
-        <v>0.04207885644634683</v>
+        <v>0.01710395</v>
       </c>
       <c r="U5" t="n">
-        <v>0.001131590333908394</v>
+        <v>0.0002000566242373246</v>
       </c>
       <c r="V5" t="n">
-        <v>0.06470807236417582</v>
+        <v>0.182537352102945</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001055332713731822</v>
+        <v>0.0008498775092939</v>
       </c>
       <c r="X5" t="n">
-        <v>0.008484269084204868</v>
+        <v>0.01938059571365583</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.000138967010718943</v>
+        <v>0.0001711673473277117</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.02633251720634219</v>
+        <v>0.007550000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0008727365038667867</v>
+        <v>5.319774431308166e-05</v>
       </c>
     </row>
     <row r="6">
@@ -2220,82 +2220,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02424811529871204</v>
+        <v>0.02362665771231898</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008645287299085092</v>
+        <v>0.0005859201170830681</v>
       </c>
       <c r="D6" t="n">
-        <v>0.007716958834699766</v>
+        <v>0.08302759419905351</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0001316633561996699</v>
+        <v>0.001813911594935393</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03104919598411397</v>
+        <v>0.05565067185658808</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001090426703202142</v>
+        <v>0.001900056560124494</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02120068846471344</v>
+        <v>0.013776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008093541882072355</v>
+        <v>0.0003145536520213997</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6659889502762431</v>
+        <v>0.03484500531700525</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03482127475044003</v>
+        <v>0.0008601289290613518</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03893214311708732</v>
+        <v>0.03459487619056252</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001064710248937368</v>
+        <v>0.001305794688770838</v>
       </c>
       <c r="N6" t="n">
-        <v>0.01234141366124776</v>
+        <v>0.04313471569485684</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0003224133873498045</v>
+        <v>0.0007588721452912134</v>
       </c>
       <c r="P6" t="n">
-        <v>0.01692075702532481</v>
+        <v>0.02709265456124085</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0007579814691740384</v>
+        <v>0.000728352546861628</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0192716852222211</v>
+        <v>0.011096</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0008149352296334703</v>
+        <v>0.0002668782493947369</v>
       </c>
       <c r="T6" t="n">
-        <v>0.04936991759083723</v>
+        <v>0.01889952222222222</v>
       </c>
       <c r="U6" t="n">
-        <v>0.001686742432993978</v>
+        <v>0.0006038857322313488</v>
       </c>
       <c r="V6" t="n">
-        <v>0.07545666524418279</v>
+        <v>0.3405389066413335</v>
       </c>
       <c r="W6" t="n">
-        <v>0.002177853769653444</v>
+        <v>0.0484253301895733</v>
       </c>
       <c r="X6" t="n">
-        <v>0.009958141972447395</v>
+        <v>0.02160004315948601</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002513569821480511</v>
+        <v>0.0006277338471386018</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.03105900535315279</v>
+        <v>0.008428000000000001</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.001033456334925518</v>
+        <v>8.715503427800367e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2305,82 +2305,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02422816046507405</v>
+        <v>0.02359817917271787</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008949323644260387</v>
+        <v>0.0005972360458618633</v>
       </c>
       <c r="D7" t="n">
-        <v>0.007707610281265403</v>
+        <v>0.08308580709816156</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0001351780462963014</v>
+        <v>0.00186155507906833</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0310313627995379</v>
+        <v>0.05553476077250308</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001119247822673038</v>
+        <v>0.001996119351056849</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02117772379026022</v>
+        <v>0.013872</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008346732811237843</v>
+        <v>0.0003125635935293803</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6494732965009208</v>
+        <v>0.03476972145791789</v>
       </c>
       <c r="K7" t="n">
-        <v>0.003314295010172298</v>
+        <v>0.0009061044756801674</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03888621993394122</v>
+        <v>0.03485837924100365</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001097538622618984</v>
+        <v>0.001362808692816009</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01232763684566027</v>
+        <v>0.04313658840895578</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0003470913299041003</v>
+        <v>0.0007661673493025447</v>
       </c>
       <c r="P7" t="n">
-        <v>0.01690509136458437</v>
+        <v>0.02717015080419333</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007795643096233793</v>
+        <v>0.0007159849041450695</v>
       </c>
       <c r="R7" t="n">
-        <v>0.01924292032107742</v>
+        <v>0.011048</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0008490115965352092</v>
+        <v>0.000335225297374765</v>
       </c>
       <c r="T7" t="n">
-        <v>0.04925095230685028</v>
+        <v>0.01889293888888889</v>
       </c>
       <c r="U7" t="n">
-        <v>0.001754587401639708</v>
+        <v>0.0006037735248081508</v>
       </c>
       <c r="V7" t="n">
-        <v>0.07535440309897826</v>
+        <v>0.3366611969945591</v>
       </c>
       <c r="W7" t="n">
-        <v>0.002164930841793416</v>
+        <v>0.001947984179267636</v>
       </c>
       <c r="X7" t="n">
-        <v>0.009943381098603665</v>
+        <v>0.02155509809460822</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002670188585883242</v>
+        <v>0.0006465742612000315</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03100485074262258</v>
+        <v>0.008433000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001089203832950796</v>
+        <v>9.703607576566566e-05</v>
       </c>
     </row>
   </sheetData>
@@ -2486,43 +2486,43 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.003578084234066344</v>
+        <v>0.001717588769611891</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01789042117033172</v>
+        <v>0.008587943848059455</v>
       </c>
       <c r="E2" t="n">
-        <v>0.01023140501979605</v>
+        <v>0.006438234329651818</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0077090321779103</v>
+        <v>0.005733553537021745</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00253447633246366</v>
+        <v>0.001635012386457474</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0253447633246366</v>
+        <v>0.01635012386457473</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01266596345649475</v>
+        <v>0.008911793742130327</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008730898248229594</v>
+        <v>0.006733186530874393</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001677226984718599</v>
+        <v>0.001288191577208918</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03354453969437197</v>
+        <v>0.02576383154417837</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01467125029140247</v>
+        <v>0.01129534725635893</v>
       </c>
       <c r="N2" t="n">
-        <v>0.009247300324446997</v>
+        <v>0.007388570435517538</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00147329650092081</v>
+        <v>0.0008636324380343726</v>
       </c>
     </row>
     <row r="3">
@@ -2537,43 +2537,43 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.005194805194805195</v>
+        <v>0.003769140164899883</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02597402597402598</v>
+        <v>0.01884570082449941</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01171934753093544</v>
+        <v>0.01167809281338608</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007142857142857142</v>
+        <v>0.009344326658814291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.003246753246753247</v>
+        <v>0.003651354534746761</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03246753246753246</v>
+        <v>0.03651354534746761</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01390010098513592</v>
+        <v>0.01735438941774113</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008089826839826838</v>
+        <v>0.0116654514181016</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002597402597402597</v>
+        <v>0.00265017667844523</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05194805194805195</v>
+        <v>0.0530035335689046</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01898087627366793</v>
+        <v>0.02140357752808297</v>
       </c>
       <c r="N3" t="n">
-        <v>0.009568035203061941</v>
+        <v>0.01271147917512061</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00147329650092081</v>
+        <v>0.0008636324380343726</v>
       </c>
     </row>
     <row r="4">
@@ -2588,43 +2588,43 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.004545454545454545</v>
+        <v>0.00447585394581861</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.02237926972909305</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01472586078445454</v>
+        <v>0.0140037704446137</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01212121212121212</v>
+        <v>0.01126815861798194</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003246753246753247</v>
+        <v>0.003886925795053004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03246753246753246</v>
+        <v>0.03886925795053003</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01777087064301607</v>
+        <v>0.01927554790991716</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01331555349412492</v>
+        <v>0.01341026791556827</v>
       </c>
       <c r="K4" t="n">
-        <v>0.002597402597402597</v>
+        <v>0.002296819787985866</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05194805194805195</v>
+        <v>0.04593639575971731</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02247539841510653</v>
+        <v>0.02102188707319875</v>
       </c>
       <c r="N4" t="n">
-        <v>0.01449678501239556</v>
+        <v>0.0138688945388778</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2895764272559853</v>
+        <v>0.3823300803178167</v>
       </c>
     </row>
     <row r="5">
@@ -2639,43 +2639,43 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.002597402597402597</v>
+        <v>0.004004711425206125</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01298701298701299</v>
+        <v>0.02002355712603062</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0109962753481641</v>
+        <v>0.01446155640888927</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01038961038961039</v>
+        <v>0.01256380054966627</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.00353356890459364</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02272727272727273</v>
+        <v>0.0353356890459364</v>
       </c>
       <c r="I5" t="n">
-        <v>0.014080133159148</v>
+        <v>0.0194678968412674</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01162002679859823</v>
+        <v>0.01466197393759231</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001948051948051948</v>
+        <v>0.002532391048292109</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03896103896103896</v>
+        <v>0.05064782096584217</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01816271011542865</v>
+        <v>0.02328468242530527</v>
       </c>
       <c r="N5" t="n">
-        <v>0.01272972574727128</v>
+        <v>0.01568045436783745</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2780110497237569</v>
+        <v>0.3669574229208049</v>
       </c>
     </row>
     <row r="6">
@@ -2690,43 +2690,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.001948051948051948</v>
+        <v>0.002120141342756184</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00974025974025974</v>
+        <v>0.01060070671378092</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00405261663435496</v>
+        <v>0.007088083110489987</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.005928543384373773</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009740259740259741</v>
+        <v>0.002120141342756184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00974025974025974</v>
+        <v>0.02120141342756184</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00405261663435496</v>
+        <v>0.01065921872531582</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.007487333370725596</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0004870129870129871</v>
+        <v>0.001295641931684335</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00974025974025974</v>
+        <v>0.02591283863368669</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00405261663435496</v>
+        <v>0.01191385473056633</v>
       </c>
       <c r="N6" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.007865709411645808</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2805156537753223</v>
+        <v>0.3653165212885396</v>
       </c>
     </row>
     <row r="7">
@@ -2741,43 +2741,43 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.003246753246753247</v>
+        <v>0.00612485276796231</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01623376623376623</v>
+        <v>0.03062426383981154</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01276193687686166</v>
+        <v>0.01877803155464667</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01163419913419913</v>
+        <v>0.0149195131527287</v>
       </c>
       <c r="G7" t="n">
-        <v>0.003246753246753247</v>
+        <v>0.003651354534746761</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03246753246753246</v>
+        <v>0.03651354534746761</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01839598956514327</v>
+        <v>0.02066677029653347</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0141852195423624</v>
+        <v>0.01569166339484361</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002272727272727273</v>
+        <v>0.002237926972909305</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.0447585394581861</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02161656148501737</v>
+        <v>0.02271636599538594</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0150387519748422</v>
+        <v>0.01623475218361936</v>
       </c>
       <c r="O7" t="n">
-        <v>0.289134438305709</v>
+        <v>0.3799550911132222</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/final_results.xlsx
+++ b/results/tables/final_results.xlsx
@@ -1269,43 +1269,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001496158511928831</v>
+        <v>0.00151637687019814</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003000012448051267</v>
+        <v>0.003172780702097321</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002458753996436174</v>
+        <v>0.002588755605111364</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00155855461203217</v>
+        <v>0.001672395201509637</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001344520824909017</v>
+        <v>0.001415285078851597</v>
       </c>
       <c r="G2" t="n">
-        <v>0.005707840429338238</v>
+        <v>0.006046716676118818</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003400300959517137</v>
+        <v>0.003589697196296889</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001844273087617878</v>
+        <v>0.001959117129014521</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001197937727456531</v>
+        <v>0.00123331985442782</v>
       </c>
       <c r="K2" t="n">
-        <v>0.009968675677217572</v>
+        <v>0.01012357240523559</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004699640737174539</v>
+        <v>0.0048351201907514</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002134050779787677</v>
+        <v>0.002232967793214463</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8308575870109681</v>
+        <v>0.8380689178685552</v>
       </c>
     </row>
     <row r="3">
@@ -1315,43 +1315,43 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002102709260008087</v>
+        <v>0.001961180752122928</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004497565201788459</v>
+        <v>0.004238096270665667</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003761592244282096</v>
+        <v>0.003480350509860485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002538105989127016</v>
+        <v>0.002344009749741654</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001718560452891225</v>
+        <v>0.001698342094621917</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00759557517656754</v>
+        <v>0.007613750575100805</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004800676903066115</v>
+        <v>0.004647075386952189</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002822315665269567</v>
+        <v>0.002686485891926074</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001465830974524869</v>
+        <v>0.00148099474322685</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0128390762237946</v>
+        <v>0.01254831125531919</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006351700957954717</v>
+        <v>0.006171971399787364</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003171575265601611</v>
+        <v>0.003031812276464435</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8219189912773124</v>
+        <v>0.8201053631574402</v>
       </c>
     </row>
     <row r="4">
@@ -1364,40 +1364,40 @@
         <v>0.002446421350586333</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0053114208842601</v>
+        <v>0.005671889340411936</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004508204507064237</v>
+        <v>0.004670322549044714</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003050135912297254</v>
+        <v>0.003174984274610235</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002163364334816013</v>
+        <v>0.002082490901738779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009389888093586362</v>
+        <v>0.009517782424578373</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0059325344349327</v>
+        <v>0.006002086532848639</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00347361468587375</v>
+        <v>0.003557041998405148</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001824706833805095</v>
+        <v>0.001774160938131824</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01552943859385021</v>
+        <v>0.01538310390571407</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007778873984779219</v>
+        <v>0.007785313922847075</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003887789830443772</v>
+        <v>0.003960124035915853</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8106485879609638</v>
+        <v>0.8109940409361776</v>
       </c>
     </row>
     <row r="5">
@@ -1407,43 +1407,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00137484836231298</v>
+        <v>0.001637687019813991</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003046146861709537</v>
+        <v>0.003258978798156516</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002610325928480082</v>
+        <v>0.002904274009357442</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001771465157029249</v>
+        <v>0.00193958642224918</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001415285078851597</v>
+        <v>0.001314193287505055</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006232287492491423</v>
+        <v>0.005359966957817472</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003738102450340879</v>
+        <v>0.003567219969736958</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002084104893698505</v>
+        <v>0.002076909792424855</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001142337242215932</v>
+        <v>0.001076627577840679</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009024558842231639</v>
+        <v>0.008590226558851249</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004628532285964567</v>
+        <v>0.004525307025412016</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002265082091058871</v>
+        <v>0.002278808815915013</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8148803869073322</v>
+        <v>0.8125485793246394</v>
       </c>
     </row>
     <row r="6">
@@ -1453,43 +1453,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002082490901738779</v>
+        <v>0.002183582693085322</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00438902018265021</v>
+        <v>0.004655502122559766</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003722308129120149</v>
+        <v>0.003949614049074407</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002487475850294289</v>
+        <v>0.002663459810396729</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001809543065103114</v>
+        <v>0.001779215527699151</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007731607508658859</v>
+        <v>0.007567218470685106</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004894719988802928</v>
+        <v>0.004942968376887366</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002823336834996088</v>
+        <v>0.002941627857505045</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001496158511928831</v>
+        <v>0.001450667205822887</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01249081705857337</v>
+        <v>0.01206977294493957</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00631172704427603</v>
+        <v>0.006286016511769336</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003132971335018225</v>
+        <v>0.003228947361921474</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7945850246135245</v>
+        <v>0.7935918473097849</v>
       </c>
     </row>
     <row r="7">
@@ -1499,43 +1499,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002567731500202184</v>
+        <v>0.002486858067124949</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005598977554499746</v>
+        <v>0.005130042844883321</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004629119585232916</v>
+        <v>0.004394942975533268</v>
       </c>
       <c r="E7" t="n">
-        <v>0.003079115559149931</v>
+        <v>0.002897009929460395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002153255155681359</v>
+        <v>0.002001617468661545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.009231189180397784</v>
+        <v>0.008629232521466199</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00592023168895525</v>
+        <v>0.005548077780066551</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003463295121705959</v>
+        <v>0.003220954104785195</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001683178325919935</v>
+        <v>0.001708451273756571</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0144426280058079</v>
+        <v>0.01500678197806737</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007443007940635791</v>
+        <v>0.007396244848091133</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003806086133282894</v>
+        <v>0.003634932477449394</v>
       </c>
       <c r="N7" t="n">
-        <v>0.802789532774851</v>
+        <v>0.8012781760082909</v>
       </c>
     </row>
     <row r="8">
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002325111200970481</v>
+        <v>0.002507076425394258</v>
       </c>
       <c r="C8" t="n">
-        <v>0.004839709879195144</v>
+        <v>0.005144990992039489</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00415993096832604</v>
+        <v>0.004542636192687672</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002834529586197601</v>
+        <v>0.003114413442961765</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001799433885968459</v>
+        <v>0.001900525677315002</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007247624064371426</v>
+        <v>0.007468803851375124</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005021529964821376</v>
+        <v>0.005356680048706607</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003085293199815757</v>
+        <v>0.00331386514034108</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001496158511928831</v>
+        <v>0.001556813586736757</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0126520975465845</v>
+        <v>0.01255512285955819</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006571081748048878</v>
+        <v>0.006861049278719345</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003433667816758336</v>
+        <v>0.00364288900647574</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8022713533120304</v>
+        <v>0.8080576906468607</v>
       </c>
     </row>
     <row r="9">
@@ -1591,43 +1591,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002689041649818035</v>
+        <v>0.002567731500202183</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005730722901823339</v>
+        <v>0.005079159271554791</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004683065840744698</v>
+        <v>0.004321025217617272</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00310691580177023</v>
+        <v>0.002874208114301118</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002153255155681359</v>
+        <v>0.002234128588758593</v>
       </c>
       <c r="G9" t="n">
-        <v>0.008948780482469117</v>
+        <v>0.009202367974879114</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005795402905564295</v>
+        <v>0.005806577239646609</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003412991846968677</v>
+        <v>0.003331896853745317</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001733724221593207</v>
+        <v>0.001743833400727861</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0138707927706198</v>
+        <v>0.01418876119235545</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007279241180607601</v>
+        <v>0.007301629021961542</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003732327569352736</v>
+        <v>0.003653656258712644</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7910441316175836</v>
+        <v>0.80326453061577</v>
       </c>
     </row>
     <row r="10">
@@ -1637,43 +1637,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002689041649818035</v>
+        <v>0.002668823291548726</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005384779803269693</v>
+        <v>0.005619670990179634</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004716785118996147</v>
+        <v>0.004861481924902577</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003206098081502449</v>
+        <v>0.003350069641011816</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002153255155681359</v>
+        <v>0.002365547917509098</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008858186970869918</v>
+        <v>0.009461646272460213</v>
       </c>
       <c r="H10" t="n">
-        <v>0.00588313325111972</v>
+        <v>0.006284310365612768</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003512671928635767</v>
+        <v>0.003756293562564383</v>
       </c>
       <c r="J10" t="n">
-        <v>0.00176405175899717</v>
+        <v>0.001870198139911039</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01452925994101071</v>
+        <v>0.01506373451672114</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007522779196072229</v>
+        <v>0.007920195702778578</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00385416290665545</v>
+        <v>0.00410189365940089</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7972622851714311</v>
+        <v>0.806157699283185</v>
       </c>
     </row>
     <row r="11">
@@ -1744,132 +1744,132 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>P@5_mean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>P@5_std</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>NDCG@20_mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>NDCG@20_std</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>MAP@10_mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>MAP@10_std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>MAP@20_mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>MAP@20_std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>R@20_mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>R@20_std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Coverage_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Coverage_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>P@20_mean</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>P@20_std</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>R@5_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>R@5_std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>P@10_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>P@10_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>NDCG@10_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>NDCG@10_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>R@10_mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>R@10_std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>P@5_mean</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>P@5_std</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>NDCG@10_mean</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>NDCG@10_std</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>R@5_mean</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>R@5_std</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>NDCG@20_mean</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>NDCG@20_std</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>NDCG@5_mean</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>NDCG@5_std</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>P@10_mean</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>P@10_std</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>MAP@5_mean</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>MAP@5_std</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>Coverage_mean</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>Coverage_std</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>MAP@10_mean</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>MAP@10_std</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>P@20_mean</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>P@20_std</t>
         </is>
       </c>
     </row>
@@ -1880,82 +1880,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.007972256122618758</v>
+        <v>0.004776000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002576845951726161</v>
+        <v>0.0002260619384151166</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02981475611769078</v>
+        <v>0.01504054724381166</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001153452181141216</v>
+        <v>0.0006098661299870154</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01884546119394819</v>
+        <v>0.007292777069160997</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0006345557479963481</v>
+        <v>0.0003901715280611656</v>
       </c>
       <c r="H2" t="n">
-        <v>0.004448000000000001</v>
+        <v>0.008014452358860089</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0002467711490429949</v>
+        <v>0.0004022584376991164</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01163101088023312</v>
+        <v>0.02975772620324422</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0002774294891482909</v>
+        <v>0.001375258317157331</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01168364807414807</v>
+        <v>0.8102254080663268</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004914041307369717</v>
+        <v>0.002474785428490744</v>
       </c>
       <c r="N2" t="n">
-        <v>0.01491875828277999</v>
+        <v>0.002961</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0004435006535253096</v>
+        <v>8.748714191239745e-05</v>
       </c>
       <c r="P2" t="n">
-        <v>0.008976710281052586</v>
+        <v>0.0123196115682563</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0003313545578495771</v>
+        <v>0.0008144517970072996</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003646000000000001</v>
+        <v>0.003832</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001139473562659527</v>
+        <v>0.0001424640305480652</v>
       </c>
       <c r="T2" t="n">
-        <v>0.006278111111111111</v>
+        <v>0.01198094354573604</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0002611879798200316</v>
+        <v>0.0005823300531386467</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8102599533638483</v>
+        <v>0.01955807415239652</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001457467699091738</v>
+        <v>0.001166733641679197</v>
       </c>
       <c r="X2" t="n">
-        <v>0.007184216921768708</v>
+        <v>0.009285893682704074</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0002230996502546447</v>
+        <v>0.0004794437757177169</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.002922</v>
+        <v>0.006378394444444444</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0001117407714310225</v>
+        <v>0.0003589588628894874</v>
       </c>
     </row>
     <row r="3">
@@ -1965,82 +1965,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.005235541418334037</v>
+        <v>0.003144</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002453311084404361</v>
+        <v>0.0001566652482205291</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02056801382780197</v>
+        <v>0.01046889116274243</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001210380377531435</v>
+        <v>0.0004871662037146941</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01260000334957602</v>
+        <v>0.00507083246409675</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000357120447464929</v>
+        <v>0.0002935161422160106</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00292</v>
+        <v>0.005625210202459046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0001697056274847714</v>
+        <v>0.0003521352979430154</v>
       </c>
       <c r="J3" t="n">
-        <v>0.007640286298542122</v>
+        <v>0.02080831028283497</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0003663379457127028</v>
+        <v>0.0009209241698293287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007429863681324358</v>
+        <v>0.6627860782450987</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0002366149521474834</v>
+        <v>0.001665579586468629</v>
       </c>
       <c r="N3" t="n">
-        <v>0.01000311389946677</v>
+        <v>0.002046</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0004479937536443689</v>
+        <v>7.227724399837058e-05</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0057361389479189</v>
+        <v>0.008228696796624429</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0003412689261348746</v>
+        <v>0.0005185968775589616</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002444</v>
+        <v>0.002538</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0001028785691968935</v>
+        <v>5.153639490690064e-05</v>
       </c>
       <c r="T3" t="n">
-        <v>0.004009233333333333</v>
+        <v>0.008145341660808315</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0002434831341282971</v>
+        <v>0.0003046382302107758</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6629242594351844</v>
+        <v>0.01305874683583623</v>
       </c>
       <c r="W3" t="n">
-        <v>0.004588888021614309</v>
+        <v>0.0003917289158200852</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004670133582136558</v>
+        <v>0.006336387435550432</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0002553058104215972</v>
+        <v>0.0004001440661703499</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.001994</v>
+        <v>0.004455522222222221</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.712878049270461e-05</v>
+        <v>0.0003424248545121311</v>
       </c>
     </row>
     <row r="4">
@@ -2050,82 +2050,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0121534069248422</v>
+        <v>0.007252</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003938402808301826</v>
+        <v>0.0001912485294061111</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04239207772595709</v>
+        <v>0.02307297851973318</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008418803773485236</v>
+        <v>0.0005772971911317945</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02658127498137314</v>
+        <v>0.01155994138007055</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001385726006929579</v>
+        <v>0.0003823351629891658</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007000000000000001</v>
+        <v>0.01264485480368202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000317742033731768</v>
+        <v>0.0004312141765730953</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01747388410177285</v>
+        <v>0.04375011255418733</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006749975763581045</v>
+        <v>0.001387545141191765</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01710675668524391</v>
+        <v>0.02270489679592366</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0008993656963879808</v>
+        <v>0.0007653752151689963</v>
       </c>
       <c r="N4" t="n">
-        <v>0.02225875645434506</v>
+        <v>0.004604</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0004724645020128851</v>
+        <v>9.866103587536497e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01396089526908307</v>
+        <v>0.01793539202636455</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.000553028482337056</v>
+        <v>0.0007377281160781851</v>
       </c>
       <c r="R4" t="n">
-        <v>0.005528</v>
+        <v>0.00591</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002531718783751464</v>
+        <v>0.0001211610498468877</v>
       </c>
       <c r="T4" t="n">
-        <v>0.009894066666666666</v>
+        <v>0.01842602817525523</v>
       </c>
       <c r="U4" t="n">
-        <v>0.000430870670564946</v>
+        <v>0.0004021262666916314</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02237671646947059</v>
+        <v>0.02846569088278789</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0005023936288884703</v>
+        <v>0.000956873195683802</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01104135255731922</v>
+        <v>0.01447860255898189</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0004403364439361508</v>
+        <v>0.0003591992711335962</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004469000000000001</v>
+        <v>0.01026534444444444</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0001032666451474046</v>
+        <v>0.0003581878492779601</v>
       </c>
     </row>
     <row r="5">
@@ -2135,82 +2135,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02122183368171335</v>
+        <v>0.012472</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001410321589915643</v>
+        <v>0.0001423235749972568</v>
       </c>
       <c r="D5" t="n">
-        <v>0.07400286297899913</v>
+        <v>0.03889284621101038</v>
       </c>
       <c r="E5" t="n">
-        <v>0.000443498391289155</v>
+        <v>0.0009387419688506653</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04873855989098663</v>
+        <v>0.01926325555870496</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001606236475605708</v>
+        <v>0.001058890961299838</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01234</v>
+        <v>0.02115264064549989</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0002802855686616774</v>
+        <v>0.001053904115345386</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03096586053764811</v>
+        <v>0.075213519564159</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0004928012188564268</v>
+        <v>0.001552092521371712</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03096974816264175</v>
+        <v>0.182537352102945</v>
       </c>
       <c r="M5" t="n">
-        <v>0.001089694056792311</v>
+        <v>0.0009568018481912183</v>
       </c>
       <c r="N5" t="n">
-        <v>0.038576399235454</v>
+        <v>0.007660999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0002160572437444974</v>
+        <v>0.000125753727578947</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0243707630028453</v>
+        <v>0.03124302010083223</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.000355125683047624</v>
+        <v>0.001374990062586399</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009836000000000001</v>
+        <v>0.009970000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>0.000271558465159899</v>
+        <v>0.0001698234377228311</v>
       </c>
       <c r="T5" t="n">
-        <v>0.01710395</v>
+        <v>0.03112113277799018</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0002000566242373246</v>
+        <v>0.0009579667897690492</v>
       </c>
       <c r="V5" t="n">
-        <v>0.182537352102945</v>
+        <v>0.04945608314202573</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0008498775092939</v>
+        <v>0.001713648388709606</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01938059571365583</v>
+        <v>0.0243896816552361</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0001711673473277117</v>
+        <v>0.0008905508688387825</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.007550000000000001</v>
+        <v>0.01693196111111111</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.319774431308166e-05</v>
+        <v>0.001038847775419395</v>
       </c>
     </row>
     <row r="6">
@@ -2220,82 +2220,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02362665771231898</v>
+        <v>0.013964</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0005859201170830681</v>
+        <v>0.0002091506633984229</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08302759419905351</v>
+        <v>0.0434748074925624</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001813911594935393</v>
+        <v>0.0008890158101842985</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05565067185658808</v>
+        <v>0.02163868402305367</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001900056560124494</v>
+        <v>0.001023169095616741</v>
       </c>
       <c r="H6" t="n">
-        <v>0.013776</v>
+        <v>0.02373543020236861</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0003145536520213997</v>
+        <v>0.001001482738165849</v>
       </c>
       <c r="J6" t="n">
-        <v>0.03484500531700525</v>
+        <v>0.0841091617528564</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008601289290613518</v>
+        <v>0.001665410319200058</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03459487619056252</v>
+        <v>0.3542447534329389</v>
       </c>
       <c r="M6" t="n">
-        <v>0.001305794688770838</v>
+        <v>0.03457506490177391</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04313471569485684</v>
+        <v>0.008525000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0007588721452912134</v>
+        <v>0.0001218605760695391</v>
       </c>
       <c r="P6" t="n">
-        <v>0.02709265456124085</v>
+        <v>0.03514234173000212</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.000728352546861628</v>
+        <v>0.001809796588334611</v>
       </c>
       <c r="R6" t="n">
-        <v>0.011096</v>
+        <v>0.011154</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0002668782493947369</v>
+        <v>0.0001395134402127625</v>
       </c>
       <c r="T6" t="n">
-        <v>0.01889952222222222</v>
+        <v>0.03492210447717664</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0006038857322313488</v>
+        <v>0.0009605935144771423</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3405389066413335</v>
+        <v>0.05575654846345722</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0484253301895733</v>
+        <v>0.00184531580149692</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02160004315948601</v>
+        <v>0.02731873522705683</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0006277338471386018</v>
+        <v>0.0009988524923684901</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.008428000000000001</v>
+        <v>0.01899435555555555</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.715503427800367e-05</v>
+        <v>0.000985900414955728</v>
       </c>
     </row>
     <row r="7">
@@ -2305,82 +2305,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02359817917271787</v>
+        <v>0.014004</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0005972360458618633</v>
+        <v>0.0001839130229211631</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08308580709816156</v>
+        <v>0.04353315183844829</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00186155507906833</v>
+        <v>0.0008886323485779763</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05553476077250308</v>
+        <v>0.02159396188586546</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001996119351056849</v>
+        <v>0.001014335528300528</v>
       </c>
       <c r="H7" t="n">
-        <v>0.013872</v>
+        <v>0.0237287947241943</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0003125635935293803</v>
+        <v>0.001000271772851454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03476972145791789</v>
+        <v>0.08436908946403412</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009061044756801674</v>
+        <v>0.001728885073798988</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03485837924100365</v>
+        <v>0.3367216512652215</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001362808692816009</v>
+        <v>0.002785050584615863</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04313658840895578</v>
+        <v>0.008556000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0007661673493025447</v>
+        <v>0.000119808180021232</v>
       </c>
       <c r="P7" t="n">
-        <v>0.02717015080419333</v>
+        <v>0.03526245207798747</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0007159849041450695</v>
+        <v>0.00181892443768472</v>
       </c>
       <c r="R7" t="n">
-        <v>0.011048</v>
+        <v>0.011136</v>
       </c>
       <c r="S7" t="n">
-        <v>0.000335225297374765</v>
+        <v>0.0001369087287209988</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01889293888888889</v>
+        <v>0.03485420270000195</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0006037735248081508</v>
+        <v>0.0009564251447879172</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3366611969945591</v>
+        <v>0.05560678700432812</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001947984179267636</v>
+        <v>0.001805856059481376</v>
       </c>
       <c r="X7" t="n">
-        <v>0.02155509809460822</v>
+        <v>0.0273386681801471</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0006465742612000315</v>
+        <v>0.0009977431753666779</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.008433000000000001</v>
+        <v>0.01898476666666666</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.703607576566566e-05</v>
+        <v>0.0009844050397493657</v>
       </c>
     </row>
   </sheetData>

--- a/results/tables/final_results.xlsx
+++ b/results/tables/final_results.xlsx
@@ -1269,43 +1269,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00151637687019814</v>
+        <v>0.001556813586736757</v>
       </c>
       <c r="C2" t="n">
-        <v>0.003172780702097321</v>
+        <v>0.003296317113602621</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002588755605111364</v>
+        <v>0.002699342636258548</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001672395201509637</v>
+        <v>0.001791458866873343</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001415285078851597</v>
+        <v>0.001344520824909017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.006046716676118818</v>
+        <v>0.005857783127711779</v>
       </c>
       <c r="H2" t="n">
-        <v>0.003589697196296889</v>
+        <v>0.003575055656494039</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001959117129014521</v>
+        <v>0.002043877225000018</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00123331985442782</v>
+        <v>0.001152446421350586</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01012357240523559</v>
+        <v>0.009749191128383841</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0048351201907514</v>
+        <v>0.004754639555061464</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002232967793214463</v>
+        <v>0.002311470853639556</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8380689178685552</v>
+        <v>0.8321530356680197</v>
       </c>
     </row>
     <row r="3">
@@ -1318,40 +1318,40 @@
         <v>0.001961180752122928</v>
       </c>
       <c r="C3" t="n">
-        <v>0.004238096270665667</v>
+        <v>0.004365471927762311</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003480350509860485</v>
+        <v>0.003599752302495862</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002344009749741654</v>
+        <v>0.002466555465696185</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001698342094621917</v>
+        <v>0.001738778811160534</v>
       </c>
       <c r="G3" t="n">
-        <v>0.007613750575100805</v>
+        <v>0.007626217394024162</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004647075386952189</v>
+        <v>0.004756504035816905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.002686485891926074</v>
+        <v>0.002798060989907937</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00148099474322685</v>
+        <v>0.001415285078851597</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01254831125531919</v>
+        <v>0.01248064838982776</v>
       </c>
       <c r="L3" t="n">
-        <v>0.006171971399787364</v>
+        <v>0.006171291230783349</v>
       </c>
       <c r="M3" t="n">
-        <v>0.003031812276464435</v>
+        <v>0.003114774962893896</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8201053631574402</v>
+        <v>0.819069004231799</v>
       </c>
     </row>
     <row r="4">
@@ -1361,43 +1361,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002446421350586333</v>
+        <v>0.002567731500202183</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005671889340411936</v>
+        <v>0.00569914905050714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.004670322549044714</v>
+        <v>0.004674342734694518</v>
       </c>
       <c r="E4" t="n">
-        <v>0.003174984274610235</v>
+        <v>0.003107786314417936</v>
       </c>
       <c r="F4" t="n">
-        <v>0.002082490901738779</v>
+        <v>0.002193691872219976</v>
       </c>
       <c r="G4" t="n">
-        <v>0.009517782424578373</v>
+        <v>0.00963269228220962</v>
       </c>
       <c r="H4" t="n">
-        <v>0.006002086532848639</v>
+        <v>0.006069904699377269</v>
       </c>
       <c r="I4" t="n">
-        <v>0.003557041998405148</v>
+        <v>0.003523283414772208</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001774160938131824</v>
+        <v>0.001814597654670441</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01538310390571407</v>
+        <v>0.01590522900957188</v>
       </c>
       <c r="L4" t="n">
-        <v>0.007785313922847075</v>
+        <v>0.007928495870143184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.003960124035915853</v>
+        <v>0.003954631930752569</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8109940409361776</v>
+        <v>0.8113394939113913</v>
       </c>
     </row>
     <row r="5">
@@ -1407,43 +1407,43 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001637687019813991</v>
+        <v>0.001455721795390214</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003258978798156516</v>
+        <v>0.002944088201160355</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002904274009357442</v>
+        <v>0.002628241792663922</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00193958642224918</v>
+        <v>0.001775396504470504</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001314193287505055</v>
+        <v>0.001354630004043672</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005359966957817472</v>
+        <v>0.005678627609274368</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003567219969736958</v>
+        <v>0.003562137861487847</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002076909792424855</v>
+        <v>0.002023516264647867</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001076627577840679</v>
+        <v>0.001152446421350586</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008590226558851249</v>
+        <v>0.009165076910769239</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004525307025412016</v>
+        <v>0.004626348353284016</v>
       </c>
       <c r="M5" t="n">
-        <v>0.002278808815915013</v>
+        <v>0.002244329752366334</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8125485793246394</v>
+        <v>0.8131531220312634</v>
       </c>
     </row>
     <row r="6">
@@ -1453,43 +1453,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002183582693085322</v>
+        <v>0.002102709260008087</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004655502122559766</v>
+        <v>0.00447395536088884</v>
       </c>
       <c r="D6" t="n">
-        <v>0.003949614049074407</v>
+        <v>0.003819383555389942</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002663459810396729</v>
+        <v>0.002597048119692681</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001779215527699151</v>
+        <v>0.001718560452891225</v>
       </c>
       <c r="G6" t="n">
-        <v>0.007567218470685106</v>
+        <v>0.007521065955365588</v>
       </c>
       <c r="H6" t="n">
-        <v>0.004942968376887366</v>
+        <v>0.004858377165290759</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002941627857505045</v>
+        <v>0.002900019759892095</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001450667205822887</v>
+        <v>0.00151637687019814</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01206977294493957</v>
+        <v>0.01241644728453542</v>
       </c>
       <c r="L6" t="n">
-        <v>0.006286016511769336</v>
+        <v>0.006365706914626186</v>
       </c>
       <c r="M6" t="n">
-        <v>0.003228947361921474</v>
+        <v>0.003227014417556096</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7935918473097849</v>
+        <v>0.7965713792210035</v>
       </c>
     </row>
     <row r="7">
@@ -1499,43 +1499,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002486858067124949</v>
+        <v>0.002426202992317024</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005130042844883321</v>
+        <v>0.005195932794339314</v>
       </c>
       <c r="D7" t="n">
-        <v>0.004394942975533268</v>
+        <v>0.004403794226977326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002897009929460395</v>
+        <v>0.002955081547378353</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002001617468661545</v>
+        <v>0.00206227254346947</v>
       </c>
       <c r="G7" t="n">
-        <v>0.008629232521466199</v>
+        <v>0.009096530577220353</v>
       </c>
       <c r="H7" t="n">
-        <v>0.005548077780066551</v>
+        <v>0.005770811592480136</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003220954104785195</v>
+        <v>0.003381743731774059</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001708451273756571</v>
+        <v>0.00169328750505459</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01500678197806737</v>
+        <v>0.01455775524430875</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007396244848091133</v>
+        <v>0.007411630775953218</v>
       </c>
       <c r="M7" t="n">
-        <v>0.003634932477449394</v>
+        <v>0.003756731386490633</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8012781760082909</v>
+        <v>0.8006304516797651</v>
       </c>
     </row>
     <row r="8">
@@ -1545,43 +1545,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002507076425394258</v>
+        <v>0.002082490901738779</v>
       </c>
       <c r="C8" t="n">
-        <v>0.005144990992039489</v>
+        <v>0.004345886472904036</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004542636192687672</v>
+        <v>0.003884429578547367</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003114413442961765</v>
+        <v>0.002735965089634721</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001900525677315002</v>
+        <v>0.00172866963202588</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007468803851375124</v>
+        <v>0.007014377495017542</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005356680048706607</v>
+        <v>0.004856967719658742</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00331386514034108</v>
+        <v>0.003029926914378997</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001556813586736757</v>
+        <v>0.001475940153659523</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01255512285955819</v>
+        <v>0.0118795403418019</v>
       </c>
       <c r="L8" t="n">
-        <v>0.006861049278719345</v>
+        <v>0.006319861241164381</v>
       </c>
       <c r="M8" t="n">
-        <v>0.00364288900647574</v>
+        <v>0.003345446602646703</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8080576906468607</v>
+        <v>0.7982554624751705</v>
       </c>
     </row>
     <row r="9">
@@ -1591,43 +1591,43 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002567731500202183</v>
+        <v>0.002203801051354631</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005079159271554791</v>
+        <v>0.004672464282920633</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004321025217617272</v>
+        <v>0.004156636611746845</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002874208114301118</v>
+        <v>0.002944607314552725</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002234128588758593</v>
+        <v>0.001920744035584311</v>
       </c>
       <c r="G9" t="n">
-        <v>0.009202367974879114</v>
+        <v>0.007795629165887148</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005806577239646609</v>
+        <v>0.005313723048250884</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003331896853745317</v>
+        <v>0.003278039733887894</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001743833400727861</v>
+        <v>0.001627577840679337</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01418876119235545</v>
+        <v>0.01278066724452272</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007301629021961542</v>
+        <v>0.006829164431491465</v>
       </c>
       <c r="M9" t="n">
-        <v>0.003653656258712644</v>
+        <v>0.003598381107304433</v>
       </c>
       <c r="N9" t="n">
-        <v>0.80326453061577</v>
+        <v>0.8000690905950427</v>
       </c>
     </row>
     <row r="10">
@@ -1637,43 +1637,43 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.002668823291548726</v>
+        <v>0.002689041649818035</v>
       </c>
       <c r="C10" t="n">
-        <v>0.005619670990179634</v>
+        <v>0.005330864503002617</v>
       </c>
       <c r="D10" t="n">
-        <v>0.004861481924902577</v>
+        <v>0.004841891931198518</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003350069641011816</v>
+        <v>0.00337638158781507</v>
       </c>
       <c r="F10" t="n">
-        <v>0.002365547917509098</v>
+        <v>0.002183582693085322</v>
       </c>
       <c r="G10" t="n">
-        <v>0.009461646272460213</v>
+        <v>0.008867543845177081</v>
       </c>
       <c r="H10" t="n">
-        <v>0.006284310365612768</v>
+        <v>0.006040261357198566</v>
       </c>
       <c r="I10" t="n">
-        <v>0.003756293562564383</v>
+        <v>0.003703313943780025</v>
       </c>
       <c r="J10" t="n">
-        <v>0.001870198139911039</v>
+        <v>0.001804488475535787</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01506373451672114</v>
+        <v>0.01512898090814704</v>
       </c>
       <c r="L10" t="n">
-        <v>0.007920195702778578</v>
+        <v>0.007837600577793287</v>
       </c>
       <c r="M10" t="n">
-        <v>0.00410189365940089</v>
+        <v>0.004090379326904334</v>
       </c>
       <c r="N10" t="n">
-        <v>0.806157699283185</v>
+        <v>0.7965281975991019</v>
       </c>
     </row>
     <row r="11">
@@ -1744,132 +1744,132 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>NDCG@5_mean</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>NDCG@5_std</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P@10_mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>P@10_std</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>P@20_mean</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>P@20_std</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>R@5_mean</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>R@5_std</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>P@5_mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>P@5_std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>NDCG@10_mean</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>NDCG@10_std</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>NDCG@20_mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>NDCG@20_std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>R@10_mean</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>R@10_std</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>MAP@5_mean</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>MAP@5_std</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>MAP@20_mean</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>MAP@20_std</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>MAP@10_mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>MAP@10_std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>MAP@20_mean</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>MAP@20_std</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>R@20_mean</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>R@20_std</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Coverage_mean</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Coverage_std</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>P@20_mean</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>P@20_std</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>R@5_mean</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>R@5_std</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>P@10_mean</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>P@10_std</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>NDCG@10_mean</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>NDCG@10_std</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>R@10_mean</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>R@10_std</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>NDCG@5_mean</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>NDCG@5_std</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>MAP@5_mean</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>MAP@5_std</t>
         </is>
       </c>
     </row>
@@ -1880,82 +1880,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.004776000000000001</v>
+        <v>0.008661255279951206</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0002260619384151166</v>
+        <v>0.0003505848024032393</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01504054724381166</v>
+        <v>0.003898</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0006098661299870154</v>
+        <v>6.305553108173784e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0.007292777069160997</v>
+        <v>0.003021</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0003901715280611656</v>
+        <v>6.335613624582877e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008014452358860089</v>
+        <v>0.01120051694504326</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004022584376991164</v>
+        <v>0.0002943551788107228</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02975772620324422</v>
+        <v>0.004624000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001375258317157331</v>
+        <v>0.0001498799519615615</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8102254080663268</v>
+        <v>0.0116106345473517</v>
       </c>
       <c r="M2" t="n">
-        <v>0.002474785428490744</v>
+        <v>0.0003405430800659635</v>
       </c>
       <c r="N2" t="n">
-        <v>0.002961</v>
+        <v>0.01478494705627748</v>
       </c>
       <c r="O2" t="n">
-        <v>8.748714191239745e-05</v>
+        <v>0.0005299030548926226</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0123196115682563</v>
+        <v>0.01908618784358916</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0008144517970072996</v>
+        <v>0.0003536283268166505</v>
       </c>
       <c r="R2" t="n">
-        <v>0.003832</v>
+        <v>0.005873722222222221</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0001424640305480652</v>
+        <v>0.0003582767715910815</v>
       </c>
       <c r="T2" t="n">
-        <v>0.01198094354573604</v>
+        <v>0.007626062433960636</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0005823300531386467</v>
+        <v>0.0004000508678617415</v>
       </c>
       <c r="V2" t="n">
-        <v>0.01955807415239652</v>
+        <v>0.006880970370370371</v>
       </c>
       <c r="W2" t="n">
-        <v>0.001166733641679197</v>
+        <v>0.0003501076750710789</v>
       </c>
       <c r="X2" t="n">
-        <v>0.009285893682704074</v>
+        <v>0.02971821233753513</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0004794437757177169</v>
+        <v>0.001153149852297166</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.006378394444444444</v>
+        <v>0.8105622247171604</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0003589588628894874</v>
+        <v>0.001486351320021808</v>
       </c>
     </row>
     <row r="3">
@@ -1965,82 +1965,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.003144</v>
+        <v>0.005692338684417279</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0001566652482205291</v>
+        <v>0.0006507794389223981</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01046889116274243</v>
+        <v>0.002478</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004871662037146941</v>
+        <v>0.000117881296226331</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00507083246409675</v>
+        <v>0.00203</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0002935161422160106</v>
+        <v>7.674633541739953e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005625210202459046</v>
+        <v>0.007405713207114523</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0003521352979430154</v>
+        <v>0.0006901930789511697</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02080831028283497</v>
+        <v>0.002952000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009209241698293287</v>
+        <v>0.0002711752201068526</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6627860782450987</v>
+        <v>0.007548663676411422</v>
       </c>
       <c r="M3" t="n">
-        <v>0.001665579586468629</v>
+        <v>0.0006086375199128511</v>
       </c>
       <c r="N3" t="n">
-        <v>0.002046</v>
+        <v>0.009941844717360255</v>
       </c>
       <c r="O3" t="n">
-        <v>7.227724399837058e-05</v>
+        <v>0.0005477292608625127</v>
       </c>
       <c r="P3" t="n">
-        <v>0.008228696796624429</v>
+        <v>0.01231608705342645</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.0005185968775589616</v>
+        <v>0.0005989509757636463</v>
       </c>
       <c r="R3" t="n">
-        <v>0.002538</v>
+        <v>0.0039232</v>
       </c>
       <c r="S3" t="n">
-        <v>5.153639490690064e-05</v>
+        <v>0.0005314176176819093</v>
       </c>
       <c r="T3" t="n">
-        <v>0.008145341660808315</v>
+        <v>0.005130289935979826</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003046382302107758</v>
+        <v>0.0004941776973174985</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01305874683583623</v>
+        <v>0.004563060345804988</v>
       </c>
       <c r="W3" t="n">
-        <v>0.0003917289158200852</v>
+        <v>0.0005166787643778412</v>
       </c>
       <c r="X3" t="n">
-        <v>0.006336387435550432</v>
+        <v>0.02039496240554251</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0004001440661703499</v>
+        <v>0.0009520524361061337</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.004455522222222221</v>
+        <v>0.6642715260385181</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0003424248545121311</v>
+        <v>0.002278975296929445</v>
       </c>
     </row>
     <row r="4">
@@ -2050,82 +2050,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007252</v>
+        <v>0.0143679180569616</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001912485294061111</v>
+        <v>0.0006558299746258316</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02307297851973318</v>
+        <v>0.005752000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0005772971911317945</v>
+        <v>0.0002940340116381093</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01155994138007055</v>
+        <v>0.004557</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003823351629891658</v>
+        <v>0.0002285738392730011</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01264485480368202</v>
+        <v>0.01758940177698232</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0004312141765730953</v>
+        <v>0.0005912067914030163</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04375011255418733</v>
+        <v>0.007308</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001387545141191765</v>
+        <v>0.0003547618919782668</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02270489679592366</v>
+        <v>0.0178518441466146</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0007653752151689963</v>
+        <v>0.000960154217283622</v>
       </c>
       <c r="N4" t="n">
-        <v>0.004604</v>
+        <v>0.02260241015933793</v>
       </c>
       <c r="O4" t="n">
-        <v>9.866103587536497e-05</v>
+        <v>0.001289208912476313</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01793539202636455</v>
+        <v>0.02689461734641243</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0007377281160781851</v>
+        <v>0.00144961917946371</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00591</v>
+        <v>0.01011075555555556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0001211610498468877</v>
+        <v>0.000469504899263148</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01842602817525523</v>
+        <v>0.01232461168861772</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0004021262666916314</v>
+        <v>0.0006851029976910813</v>
       </c>
       <c r="V4" t="n">
-        <v>0.02846569088278789</v>
+        <v>0.01122078167359536</v>
       </c>
       <c r="W4" t="n">
-        <v>0.000956873195683802</v>
+        <v>0.0005935565872974813</v>
       </c>
       <c r="X4" t="n">
-        <v>0.01447860255898189</v>
+        <v>0.04257208746709887</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0003591992711335962</v>
+        <v>0.002773973587384882</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.01026534444444444</v>
+        <v>0.02231626219880819</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.0003581878492779601</v>
+        <v>0.0004295649059658309</v>
       </c>
     </row>
     <row r="5">
@@ -2135,82 +2135,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.012472</v>
+        <v>0.02423332978611827</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001423235749972568</v>
+        <v>0.001339115276428817</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03889284621101038</v>
+        <v>0.009915999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009387419688506653</v>
+        <v>0.0002942515930288237</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01926325555870496</v>
+        <v>0.007608000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001058890961299838</v>
+        <v>0.0001755448660599335</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02115264064549989</v>
+        <v>0.03102231700945586</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001053904115345386</v>
+        <v>0.001889766912889034</v>
       </c>
       <c r="J5" t="n">
-        <v>0.075213519564159</v>
+        <v>0.01246</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001552092521371712</v>
+        <v>0.0005306599664568627</v>
       </c>
       <c r="L5" t="n">
-        <v>0.182537352102945</v>
+        <v>0.03080551281818959</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0009568018481912183</v>
+        <v>0.001291324378411734</v>
       </c>
       <c r="N5" t="n">
-        <v>0.007660999999999999</v>
+        <v>0.03844557383857747</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000125753727578947</v>
+        <v>0.001335882165143119</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03124302010083223</v>
+        <v>0.04867475893982964</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001374990062586399</v>
+        <v>0.001987821007560349</v>
       </c>
       <c r="R5" t="n">
-        <v>0.009970000000000001</v>
+        <v>0.01682893333333333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001698234377228311</v>
+        <v>0.001053086895779133</v>
       </c>
       <c r="T5" t="n">
-        <v>0.03112113277799018</v>
+        <v>0.02094302432744257</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0009579667897690492</v>
+        <v>0.001024931957233</v>
       </c>
       <c r="V5" t="n">
-        <v>0.04945608314202573</v>
+        <v>0.01908241633597883</v>
       </c>
       <c r="W5" t="n">
-        <v>0.001713648388709606</v>
+        <v>0.001019534697039349</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0243896816552361</v>
+        <v>0.07384867060070796</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0008905508688387825</v>
+        <v>0.002181595269349044</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.01693196111111111</v>
+        <v>0.1834009845409794</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.001038847775419395</v>
+        <v>0.0005430593288630287</v>
       </c>
     </row>
     <row r="6">
@@ -2220,82 +2220,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.013964</v>
+        <v>0.02729137791085216</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002091506633984229</v>
+        <v>0.001154162808927625</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0434748074925624</v>
+        <v>0.011176</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008890158101842985</v>
+        <v>0.0002142521878534726</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02163868402305367</v>
+        <v>0.008507999999999998</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001023169095616741</v>
+        <v>0.0001019117265087786</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02373543020236861</v>
+        <v>0.03470991306786368</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001001482738165849</v>
+        <v>0.00169597533929675</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0841091617528564</v>
+        <v>0.014</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001665410319200058</v>
+        <v>0.000455016483217916</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3542447534329389</v>
+        <v>0.03483727468578922</v>
       </c>
       <c r="M6" t="n">
-        <v>0.03457506490177391</v>
+        <v>0.001150776568522161</v>
       </c>
       <c r="N6" t="n">
-        <v>0.008525000000000001</v>
+        <v>0.04326489281901232</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001218605760695391</v>
+        <v>0.001110393274358551</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03514234173000212</v>
+        <v>0.05508350717177959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.001809796588334611</v>
+        <v>0.001931221573807867</v>
       </c>
       <c r="R6" t="n">
-        <v>0.011154</v>
+        <v>0.01903568333333333</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001395134402127625</v>
+        <v>0.0008607515296903038</v>
       </c>
       <c r="T6" t="n">
-        <v>0.03492210447717664</v>
+        <v>0.02370906508781364</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0009605935144771423</v>
+        <v>0.0008737674621398181</v>
       </c>
       <c r="V6" t="n">
-        <v>0.05575654846345722</v>
+        <v>0.02163325431783824</v>
       </c>
       <c r="W6" t="n">
-        <v>0.00184531580149692</v>
+        <v>0.0008854589062604482</v>
       </c>
       <c r="X6" t="n">
-        <v>0.02731873522705683</v>
+        <v>0.08280344824782315</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0009988524923684901</v>
+        <v>0.002155188850356605</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.01899435555555555</v>
+        <v>0.3230589860955178</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.000985900414955728</v>
+        <v>0.02849724803235283</v>
       </c>
     </row>
     <row r="7">
@@ -2305,82 +2305,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.014004</v>
+        <v>0.02719788855041286</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001839130229211631</v>
+        <v>0.001157860069618703</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04353315183844829</v>
+        <v>0.011188</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008886323485779763</v>
+        <v>0.0002261327044016407</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02159396188586546</v>
+        <v>0.008531</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001014335528300528</v>
+        <v>0.0001201415831425574</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0237287947241943</v>
+        <v>0.03470638695419241</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001000271772851454</v>
+        <v>0.001696606159801233</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08436908946403412</v>
+        <v>0.014016</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001728885073798988</v>
+        <v>0.0004610249450951652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3367216512652215</v>
+        <v>0.03475536844509571</v>
       </c>
       <c r="M7" t="n">
-        <v>0.002785050584615863</v>
+        <v>0.001148503639816801</v>
       </c>
       <c r="N7" t="n">
-        <v>0.008556000000000001</v>
+        <v>0.04326085058359448</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000119808180021232</v>
+        <v>0.001111062940156465</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03526245207798747</v>
+        <v>0.05509071424248666</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00181892443768472</v>
+        <v>0.001929398588749793</v>
       </c>
       <c r="R7" t="n">
-        <v>0.011136</v>
+        <v>0.01891522777777778</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0001369087287209988</v>
+        <v>0.0008779344226262572</v>
       </c>
       <c r="T7" t="n">
-        <v>0.03485420270000195</v>
+        <v>0.02361563217206586</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0009564251447879172</v>
+        <v>0.0008960168774176104</v>
       </c>
       <c r="V7" t="n">
-        <v>0.05560678700432812</v>
+        <v>0.02151861063869992</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001805856059481376</v>
+        <v>0.0009025305533554256</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0273386681801471</v>
+        <v>0.08310337731875221</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0009977431753666779</v>
+        <v>0.001955488961654227</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01898476666666666</v>
+        <v>0.3361084722342171</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0009844050397493657</v>
+        <v>0.003286186680823472</v>
       </c>
     </row>
   </sheetData>
